--- a/data/BOS_ENVANTER_SABLONU.xlsx
+++ b/data/BOS_ENVANTER_SABLONU.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SİAM2026\Desktop\kimyasal_envanter_oluşturucu\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SİAM2026\Desktop\kimyasal_envanter_oluşturucu\ONLİNE TAŞIMA İÇİN\kimyasal_envanter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E1F1308-0AC9-4C48-AD51-208429537A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3375234D-E4DA-482A-AD7F-C60679892EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -557,6 +557,108 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>304800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1026" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC24214D-A3BC-F4B4-DE99-4E09204675B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="819150" y="4667250"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>1085851</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>19499</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Resim 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96E1232D-A728-EDA4-BE3B-5AD83C638028}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="3889" t="8421" b="2104"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21755101" y="0"/>
+          <a:ext cx="1124398" cy="1104900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1195,7 +1297,7 @@
     </row>
     <row r="11" spans="1:24" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
+      <c r="B11"/>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
@@ -1238,5 +1340,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="34" orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/BOS_ENVANTER_SABLONU.xlsx
+++ b/data/BOS_ENVANTER_SABLONU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SİAM2026\Desktop\kimyasal_envanter_oluşturucu\ONLİNE TAŞIMA İÇİN\kimyasal_envanter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3375234D-E4DA-482A-AD7F-C60679892EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C377420A-45ED-43AA-9365-666A5302605C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
